--- a/GenAI/ROADMAP-GenAI.xlsx
+++ b/GenAI/ROADMAP-GenAI.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hi\Desktop\projects\python_projects\tutorial\tut_youtube\GenAI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC5A3706-73B0-48AC-BFF2-4B1CF06621FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{733DE8D6-1C83-466F-8135-6B3A515B6AC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1185" yWindow="2055" windowWidth="27615" windowHeight="13425" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1125" yWindow="1125" windowWidth="27615" windowHeight="13425" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="108">
   <si>
     <t>Week</t>
   </si>
@@ -346,6 +346,9 @@
   </si>
   <si>
     <t>Guardrails</t>
+  </si>
+  <si>
+    <t>Building first text generator</t>
   </si>
 </sst>
 </file>
@@ -689,7 +692,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H91"/>
+  <dimension ref="A1:H92"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="5"/>
@@ -874,46 +877,40 @@
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" s="4">
+        <v>1</v>
+      </c>
+      <c r="B10" s="4"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="3" t="s">
+        <v>107</v>
+      </c>
       <c r="E10" s="3"/>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="5">
-        <v>2</v>
-      </c>
-      <c r="B12" s="5">
-        <v>7</v>
-      </c>
-      <c r="C12" s="5">
-        <v>20</v>
-      </c>
-      <c r="D12" t="s">
-        <v>16</v>
-      </c>
-      <c r="E12" t="s">
-        <v>17</v>
-      </c>
-      <c r="F12" t="s">
-        <v>98</v>
-      </c>
+      <c r="F10" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E11" s="3"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="5">
         <v>2</v>
       </c>
       <c r="B13" s="5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C13" s="5">
         <v>20</v>
       </c>
       <c r="D13" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E13" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F13" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
@@ -921,19 +918,19 @@
         <v>2</v>
       </c>
       <c r="B14" s="5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C14" s="5">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D14" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E14" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F14" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
@@ -941,19 +938,19 @@
         <v>2</v>
       </c>
       <c r="B15" s="5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C15" s="5">
         <v>25</v>
       </c>
       <c r="D15" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E15" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F15" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
@@ -961,245 +958,242 @@
         <v>2</v>
       </c>
       <c r="B16" s="5">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C16" s="5">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="D16" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E16" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F16" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="D17"/>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="5">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" s="5">
+        <v>2</v>
+      </c>
+      <c r="B17" s="5">
+        <v>11</v>
+      </c>
+      <c r="C17" s="5">
+        <v>20</v>
+      </c>
+      <c r="D17" t="s">
+        <v>24</v>
+      </c>
+      <c r="E17" t="s">
+        <v>25</v>
+      </c>
+      <c r="F17" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D18"/>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="5">
         <v>3</v>
       </c>
-      <c r="B18" s="5">
+      <c r="B19" s="5">
         <v>12</v>
       </c>
-      <c r="C18" s="5">
-        <v>20</v>
-      </c>
-      <c r="D18" t="s">
+      <c r="C19" s="5">
+        <v>20</v>
+      </c>
+      <c r="D19" t="s">
         <v>26</v>
       </c>
-      <c r="E18" t="s">
+      <c r="E19" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" s="5" t="s">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B20" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="C19" s="5" t="s">
+      <c r="C20" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="D19" t="s">
+      <c r="D20" t="s">
         <v>84</v>
       </c>
-      <c r="E19" s="6" t="s">
+      <c r="E20" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="F19" s="5" t="s">
+      <c r="F20" s="5" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="5">
-        <v>3</v>
-      </c>
-      <c r="B20" s="5">
-        <v>13</v>
-      </c>
-      <c r="C20" s="5">
-        <v>20</v>
-      </c>
-      <c r="D20" t="s">
-        <v>27</v>
-      </c>
-      <c r="E20" t="s">
-        <v>28</v>
-      </c>
-      <c r="F20" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="5">
         <v>3</v>
       </c>
       <c r="B21" s="5">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="C21" s="5">
         <v>20</v>
       </c>
       <c r="D21" t="s">
-        <v>93</v>
+        <v>27</v>
       </c>
       <c r="E21" t="s">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="F21" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="5">
         <v>3</v>
       </c>
       <c r="B22" s="5">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C22" s="5">
         <v>20</v>
       </c>
       <c r="D22" t="s">
-        <v>51</v>
+        <v>93</v>
       </c>
       <c r="E22" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F22" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="5">
         <v>3</v>
       </c>
       <c r="B23" s="5">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="C23" s="5">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D23" t="s">
-        <v>29</v>
+        <v>51</v>
       </c>
       <c r="E23" t="s">
-        <v>30</v>
+        <v>52</v>
       </c>
       <c r="F23" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="5">
         <v>3</v>
       </c>
       <c r="B24" s="5">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C24" s="5">
         <v>25</v>
       </c>
       <c r="D24" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E24" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F24" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="5">
         <v>3</v>
       </c>
       <c r="B25" s="5">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C25" s="5">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="D25" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E25" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F25" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="D26"/>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" s="5">
-        <v>4</v>
-      </c>
-      <c r="B27" s="5">
-        <v>17</v>
-      </c>
-      <c r="C27" s="5">
-        <v>20</v>
-      </c>
-      <c r="D27" t="s">
-        <v>35</v>
-      </c>
-      <c r="E27" t="s">
-        <v>36</v>
-      </c>
-      <c r="F27" t="s">
-        <v>72</v>
-      </c>
-      <c r="G27" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" s="5">
+        <v>3</v>
+      </c>
+      <c r="B26" s="5">
+        <v>16</v>
+      </c>
+      <c r="C26" s="5">
+        <v>20</v>
+      </c>
+      <c r="D26" t="s">
+        <v>33</v>
+      </c>
+      <c r="E26" t="s">
+        <v>34</v>
+      </c>
+      <c r="F26" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D27"/>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="5">
         <v>4</v>
       </c>
       <c r="B28" s="5">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C28" s="5">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D28" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E28" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F28" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="G28" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="5">
         <v>4</v>
       </c>
       <c r="B29" s="5">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C29" s="5">
         <v>25</v>
       </c>
       <c r="D29" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E29" t="s">
-        <v>79</v>
+        <v>38</v>
       </c>
       <c r="F29" t="s">
         <v>74</v>
@@ -1208,127 +1202,136 @@
         <v>70</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="5">
         <v>4</v>
       </c>
       <c r="B30" s="5">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C30" s="5">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="D30" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E30" t="s">
-        <v>41</v>
+        <v>79</v>
       </c>
       <c r="F30" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G30" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="5">
         <v>4</v>
       </c>
       <c r="B31" s="5">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C31" s="5">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D31" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E31" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F31" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+        <v>73</v>
+      </c>
+      <c r="G31" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="5">
         <v>4</v>
       </c>
       <c r="B32" s="5">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C32" s="5">
         <v>25</v>
       </c>
       <c r="D32" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E32" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F32" t="s">
         <v>72</v>
       </c>
-      <c r="G32" t="s">
-        <v>70</v>
-      </c>
-      <c r="H32" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="5">
         <v>4</v>
       </c>
+      <c r="B33" s="5">
+        <v>22</v>
+      </c>
+      <c r="C33" s="5">
+        <v>25</v>
+      </c>
       <c r="D33" t="s">
+        <v>44</v>
+      </c>
+      <c r="E33" t="s">
+        <v>45</v>
+      </c>
+      <c r="F33" t="s">
+        <v>72</v>
+      </c>
+      <c r="G33" t="s">
+        <v>70</v>
+      </c>
+      <c r="H33" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" s="5">
+        <v>4</v>
+      </c>
+      <c r="D34" t="s">
         <v>103</v>
       </c>
-      <c r="F33" t="s">
+      <c r="F34" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="D34"/>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="D35"/>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="5">
-        <v>5</v>
-      </c>
-      <c r="B36" s="5">
-        <v>23</v>
-      </c>
-      <c r="C36" s="5">
-        <v>20</v>
-      </c>
-      <c r="D36" t="s">
-        <v>46</v>
-      </c>
-      <c r="E36" t="s">
-        <v>47</v>
-      </c>
-      <c r="G36" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D36"/>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" s="5">
         <v>5</v>
       </c>
+      <c r="B37" s="5">
+        <v>23</v>
+      </c>
+      <c r="C37" s="5">
+        <v>20</v>
+      </c>
       <c r="D37" t="s">
         <v>46</v>
       </c>
-      <c r="E37" s="1" t="s">
-        <v>96</v>
+      <c r="E37" t="s">
+        <v>47</v>
       </c>
       <c r="G37" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" s="5">
         <v>5</v>
       </c>
@@ -1336,155 +1339,149 @@
         <v>46</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G38" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" s="5">
         <v>5</v>
       </c>
-      <c r="B39" s="5">
-        <v>24</v>
-      </c>
-      <c r="C39" s="5">
-        <v>25</v>
-      </c>
       <c r="D39" t="s">
-        <v>48</v>
-      </c>
-      <c r="E39" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+        <v>46</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="G39" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" s="5">
         <v>5</v>
       </c>
+      <c r="B40" s="5">
+        <v>24</v>
+      </c>
+      <c r="C40" s="5">
+        <v>25</v>
+      </c>
       <c r="D40" t="s">
+        <v>48</v>
+      </c>
+      <c r="E40" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" s="5">
+        <v>5</v>
+      </c>
+      <c r="D41" t="s">
         <v>101</v>
       </c>
-      <c r="G40" t="s">
+      <c r="G41" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A42" s="5" t="s">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="B42" s="5">
+      <c r="B43" s="5">
         <v>27</v>
       </c>
-      <c r="C42" s="5">
-        <v>20</v>
-      </c>
-      <c r="D42" t="s">
+      <c r="C43" s="5">
+        <v>20</v>
+      </c>
+      <c r="D43" t="s">
         <v>53</v>
       </c>
-      <c r="E42" t="s">
+      <c r="E43" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A43" s="5" t="s">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="B43" s="5" t="s">
+      <c r="B44" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="C43" s="5" t="s">
+      <c r="C44" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="D43" t="s">
+      <c r="D44" t="s">
         <v>81</v>
       </c>
-      <c r="E43" t="s">
+      <c r="E44" t="s">
         <v>82</v>
       </c>
-      <c r="F43" s="5" t="s">
+      <c r="F44" s="5" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A44" s="5" t="s">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="B44" s="5" t="s">
+      <c r="B45" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="C44" s="5" t="s">
+      <c r="C45" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="D44" s="6" t="s">
+      <c r="D45" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="F44" s="5" t="s">
+      <c r="F45" s="5" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="D45"/>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A46" s="5">
-        <v>6</v>
-      </c>
-      <c r="B46" s="5">
-        <v>28</v>
-      </c>
-      <c r="C46" s="5">
-        <v>20</v>
-      </c>
-      <c r="D46" t="s">
-        <v>55</v>
-      </c>
-      <c r="E46" t="s">
-        <v>56</v>
-      </c>
-      <c r="F46" t="s">
-        <v>90</v>
-      </c>
-      <c r="G46" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D46"/>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" s="5">
         <v>6</v>
       </c>
       <c r="B47" s="5">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C47" s="5">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D47" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E47" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F47" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G47" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" s="5">
         <v>6</v>
       </c>
       <c r="B48" s="5">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C48" s="5">
         <v>25</v>
       </c>
       <c r="D48" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E48" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F48" t="s">
         <v>90</v>
@@ -1495,19 +1492,19 @@
         <v>6</v>
       </c>
       <c r="B49" s="5">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C49" s="5">
         <v>25</v>
       </c>
       <c r="D49" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E49" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F49" t="s">
-        <v>72</v>
+        <v>90</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
@@ -1515,22 +1512,19 @@
         <v>6</v>
       </c>
       <c r="B50" s="5">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C50" s="5">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="D50" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E50" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="F50" t="s">
         <v>72</v>
-      </c>
-      <c r="G50" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
@@ -1538,20 +1532,40 @@
         <v>6</v>
       </c>
       <c r="B51" s="5">
+        <v>32</v>
+      </c>
+      <c r="C51" s="5">
+        <v>20</v>
+      </c>
+      <c r="D51" t="s">
+        <v>63</v>
+      </c>
+      <c r="E51" t="s">
+        <v>64</v>
+      </c>
+      <c r="F51" t="s">
+        <v>72</v>
+      </c>
+      <c r="G51" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A52" s="5">
+        <v>6</v>
+      </c>
+      <c r="B52" s="5">
         <v>33</v>
       </c>
-      <c r="C51" s="5">
+      <c r="C52" s="5">
         <v>15</v>
       </c>
-      <c r="D51" t="s">
+      <c r="D52" t="s">
         <v>65</v>
       </c>
-      <c r="E51" t="s">
+      <c r="E52" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="D52"/>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="D53"/>
@@ -1669,6 +1683,9 @@
     </row>
     <row r="91" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D91"/>
+    </row>
+    <row r="92" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D92"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/GenAI/ROADMAP-GenAI.xlsx
+++ b/GenAI/ROADMAP-GenAI.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hi\Desktop\projects\python_projects\tutorial\tut_youtube\GenAI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{733DE8D6-1C83-466F-8135-6B3A515B6AC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EB8F4FA-3C22-4A85-82DB-0F4024F07AC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1125" yWindow="1125" windowWidth="27615" windowHeight="13425" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="109">
   <si>
     <t>Week</t>
   </si>
@@ -349,6 +349,9 @@
   </si>
   <si>
     <t>Building first text generator</t>
+  </si>
+  <si>
+    <t>Text summarizer using Hugging face + Gradio</t>
   </si>
 </sst>
 </file>
@@ -692,7 +695,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H92"/>
+  <dimension ref="A1:H93"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="5"/>
@@ -1306,43 +1309,41 @@
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" s="5">
+        <v>4</v>
+      </c>
       <c r="D35"/>
+      <c r="E35" t="s">
+        <v>108</v>
+      </c>
+      <c r="F35" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="D36"/>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A37" s="5">
-        <v>5</v>
-      </c>
-      <c r="B37" s="5">
-        <v>23</v>
-      </c>
-      <c r="C37" s="5">
-        <v>20</v>
-      </c>
-      <c r="D37" t="s">
-        <v>46</v>
-      </c>
-      <c r="E37" t="s">
-        <v>47</v>
-      </c>
-      <c r="G37" t="s">
-        <v>95</v>
-      </c>
+      <c r="D37"/>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" s="5">
         <v>5</v>
       </c>
+      <c r="B38" s="5">
+        <v>23</v>
+      </c>
+      <c r="C38" s="5">
+        <v>20</v>
+      </c>
       <c r="D38" t="s">
         <v>46</v>
       </c>
-      <c r="E38" s="1" t="s">
-        <v>96</v>
+      <c r="E38" t="s">
+        <v>47</v>
       </c>
       <c r="G38" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
@@ -1353,7 +1354,7 @@
         <v>46</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G39" t="s">
         <v>94</v>
@@ -1363,128 +1364,122 @@
       <c r="A40" s="5">
         <v>5</v>
       </c>
-      <c r="B40" s="5">
-        <v>24</v>
-      </c>
-      <c r="C40" s="5">
-        <v>25</v>
-      </c>
       <c r="D40" t="s">
-        <v>48</v>
-      </c>
-      <c r="E40" t="s">
-        <v>49</v>
+        <v>46</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="G40" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="5">
         <v>5</v>
       </c>
+      <c r="B41" s="5">
+        <v>24</v>
+      </c>
+      <c r="C41" s="5">
+        <v>25</v>
+      </c>
       <c r="D41" t="s">
+        <v>48</v>
+      </c>
+      <c r="E41" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" s="5">
+        <v>5</v>
+      </c>
+      <c r="D42" t="s">
         <v>101</v>
       </c>
-      <c r="G41" t="s">
+      <c r="G42" t="s">
         <v>102</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A43" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="B43" s="5">
-        <v>27</v>
-      </c>
-      <c r="C43" s="5">
-        <v>20</v>
-      </c>
-      <c r="D43" t="s">
-        <v>53</v>
-      </c>
-      <c r="E43" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="C44" s="5" t="s">
-        <v>83</v>
+        <v>105</v>
+      </c>
+      <c r="B44" s="5">
+        <v>27</v>
+      </c>
+      <c r="C44" s="5">
+        <v>20</v>
       </c>
       <c r="D44" t="s">
-        <v>81</v>
+        <v>53</v>
       </c>
       <c r="E44" t="s">
-        <v>82</v>
-      </c>
-      <c r="F44" s="5" t="s">
-        <v>73</v>
+        <v>54</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="C45" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="D45" t="s">
+        <v>81</v>
+      </c>
+      <c r="E45" t="s">
+        <v>82</v>
+      </c>
+      <c r="F45" s="5" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="B45" s="5" t="s">
+      <c r="B46" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="C45" s="5" t="s">
+      <c r="C46" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="D45" s="6" t="s">
+      <c r="D46" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="F45" s="5" t="s">
+      <c r="F46" s="5" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="D46"/>
-    </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A47" s="5">
-        <v>6</v>
-      </c>
-      <c r="B47" s="5">
-        <v>28</v>
-      </c>
-      <c r="C47" s="5">
-        <v>20</v>
-      </c>
-      <c r="D47" t="s">
-        <v>55</v>
-      </c>
-      <c r="E47" t="s">
-        <v>56</v>
-      </c>
-      <c r="F47" t="s">
-        <v>90</v>
-      </c>
-      <c r="G47" t="s">
-        <v>76</v>
-      </c>
+      <c r="D47"/>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" s="5">
         <v>6</v>
       </c>
       <c r="B48" s="5">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C48" s="5">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D48" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E48" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F48" t="s">
         <v>90</v>
+      </c>
+      <c r="G48" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
@@ -1492,16 +1487,16 @@
         <v>6</v>
       </c>
       <c r="B49" s="5">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C49" s="5">
         <v>25</v>
       </c>
       <c r="D49" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E49" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F49" t="s">
         <v>90</v>
@@ -1512,19 +1507,19 @@
         <v>6</v>
       </c>
       <c r="B50" s="5">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C50" s="5">
         <v>25</v>
       </c>
       <c r="D50" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E50" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F50" t="s">
-        <v>72</v>
+        <v>90</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
@@ -1532,22 +1527,19 @@
         <v>6</v>
       </c>
       <c r="B51" s="5">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C51" s="5">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="D51" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E51" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="F51" t="s">
         <v>72</v>
-      </c>
-      <c r="G51" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
@@ -1555,20 +1547,40 @@
         <v>6</v>
       </c>
       <c r="B52" s="5">
+        <v>32</v>
+      </c>
+      <c r="C52" s="5">
+        <v>20</v>
+      </c>
+      <c r="D52" t="s">
+        <v>63</v>
+      </c>
+      <c r="E52" t="s">
+        <v>64</v>
+      </c>
+      <c r="F52" t="s">
+        <v>72</v>
+      </c>
+      <c r="G52" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A53" s="5">
+        <v>6</v>
+      </c>
+      <c r="B53" s="5">
         <v>33</v>
       </c>
-      <c r="C52" s="5">
+      <c r="C53" s="5">
         <v>15</v>
       </c>
-      <c r="D52" t="s">
+      <c r="D53" t="s">
         <v>65</v>
       </c>
-      <c r="E52" t="s">
+      <c r="E53" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="D53"/>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="D54"/>
@@ -1686,6 +1698,9 @@
     </row>
     <row r="92" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D92"/>
+    </row>
+    <row r="93" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D93"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/GenAI/ROADMAP-GenAI.xlsx
+++ b/GenAI/ROADMAP-GenAI.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hi\Desktop\projects\python_projects\tutorial\tut_youtube\GenAI\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ash\Desktop\educational\tut_youtube\GenAI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EB8F4FA-3C22-4A85-82DB-0F4024F07AC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90744AC9-957C-417B-86BC-29D0F02CBBF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -141,9 +141,6 @@
     <t xml:space="preserve"> OpenAI API Demo </t>
   </si>
   <si>
-    <t xml:space="preserve"> Generate text, parameters (temperature etc.) </t>
-  </si>
-  <si>
     <t xml:space="preserve"> Build Chatbot </t>
   </si>
   <si>
@@ -352,6 +349,9 @@
   </si>
   <si>
     <t>Text summarizer using Hugging face + Gradio</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Generate text, parameters (temperature, tokens, etc.) </t>
   </si>
 </sst>
 </file>
@@ -722,16 +722,16 @@
         <v>1</v>
       </c>
       <c r="E1" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="G1" s="2" t="s">
-        <v>69</v>
-      </c>
       <c r="H1" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
@@ -770,42 +770,42 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
@@ -859,7 +859,7 @@
         <v>13</v>
       </c>
       <c r="F8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -886,11 +886,11 @@
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
       <c r="D10" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E10" s="3"/>
       <c r="F10" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
@@ -913,7 +913,7 @@
         <v>17</v>
       </c>
       <c r="F13" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
@@ -933,7 +933,7 @@
         <v>19</v>
       </c>
       <c r="F14" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
@@ -953,7 +953,7 @@
         <v>21</v>
       </c>
       <c r="F15" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
@@ -973,7 +973,7 @@
         <v>23</v>
       </c>
       <c r="F16" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -993,7 +993,7 @@
         <v>25</v>
       </c>
       <c r="F17" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -1013,27 +1013,27 @@
         <v>26</v>
       </c>
       <c r="E19" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="D20" t="s">
         <v>83</v>
       </c>
-      <c r="B20" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="D20" t="s">
-        <v>84</v>
-      </c>
       <c r="E20" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="F20" s="5" t="s">
         <v>91</v>
-      </c>
-      <c r="F20" s="5" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -1053,7 +1053,7 @@
         <v>28</v>
       </c>
       <c r="F21" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
@@ -1067,13 +1067,13 @@
         <v>20</v>
       </c>
       <c r="D22" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E22" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F22" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
@@ -1087,13 +1087,13 @@
         <v>20</v>
       </c>
       <c r="D23" t="s">
+        <v>50</v>
+      </c>
+      <c r="E23" t="s">
         <v>51</v>
       </c>
-      <c r="E23" t="s">
-        <v>52</v>
-      </c>
       <c r="F23" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -1113,7 +1113,7 @@
         <v>30</v>
       </c>
       <c r="F24" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
@@ -1133,7 +1133,7 @@
         <v>32</v>
       </c>
       <c r="F25" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
@@ -1153,7 +1153,7 @@
         <v>34</v>
       </c>
       <c r="F26" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
@@ -1176,10 +1176,10 @@
         <v>36</v>
       </c>
       <c r="F28" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G28" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
@@ -1196,13 +1196,13 @@
         <v>37</v>
       </c>
       <c r="E29" t="s">
-        <v>38</v>
+        <v>108</v>
       </c>
       <c r="F29" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G29" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
@@ -1216,16 +1216,16 @@
         <v>25</v>
       </c>
       <c r="D30" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E30" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F30" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G30" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
@@ -1239,16 +1239,16 @@
         <v>20</v>
       </c>
       <c r="D31" t="s">
+        <v>39</v>
+      </c>
+      <c r="E31" t="s">
         <v>40</v>
       </c>
-      <c r="E31" t="s">
-        <v>41</v>
-      </c>
       <c r="F31" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G31" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
@@ -1262,13 +1262,13 @@
         <v>25</v>
       </c>
       <c r="D32" t="s">
+        <v>41</v>
+      </c>
+      <c r="E32" t="s">
         <v>42</v>
       </c>
-      <c r="E32" t="s">
-        <v>43</v>
-      </c>
       <c r="F32" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
@@ -1282,19 +1282,19 @@
         <v>25</v>
       </c>
       <c r="D33" t="s">
+        <v>43</v>
+      </c>
+      <c r="E33" t="s">
         <v>44</v>
       </c>
-      <c r="E33" t="s">
-        <v>45</v>
-      </c>
       <c r="F33" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G33" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H33" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
@@ -1302,10 +1302,10 @@
         <v>4</v>
       </c>
       <c r="D34" t="s">
+        <v>102</v>
+      </c>
+      <c r="F34" t="s">
         <v>103</v>
-      </c>
-      <c r="F34" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
@@ -1314,10 +1314,10 @@
       </c>
       <c r="D35"/>
       <c r="E35" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F35" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
@@ -1337,13 +1337,13 @@
         <v>20</v>
       </c>
       <c r="D38" t="s">
+        <v>45</v>
+      </c>
+      <c r="E38" t="s">
         <v>46</v>
       </c>
-      <c r="E38" t="s">
-        <v>47</v>
-      </c>
       <c r="G38" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
@@ -1351,13 +1351,13 @@
         <v>5</v>
       </c>
       <c r="D39" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G39" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
@@ -1365,13 +1365,13 @@
         <v>5</v>
       </c>
       <c r="D40" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G40" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
@@ -1385,10 +1385,10 @@
         <v>25</v>
       </c>
       <c r="D41" t="s">
+        <v>47</v>
+      </c>
+      <c r="E41" t="s">
         <v>48</v>
-      </c>
-      <c r="E41" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
@@ -1396,15 +1396,15 @@
         <v>5</v>
       </c>
       <c r="D42" t="s">
+        <v>100</v>
+      </c>
+      <c r="G42" t="s">
         <v>101</v>
-      </c>
-      <c r="G42" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B44" s="5">
         <v>27</v>
@@ -1413,47 +1413,47 @@
         <v>20</v>
       </c>
       <c r="D44" t="s">
+        <v>52</v>
+      </c>
+      <c r="E44" t="s">
         <v>53</v>
-      </c>
-      <c r="E44" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D45" t="s">
+        <v>80</v>
+      </c>
+      <c r="E45" t="s">
         <v>81</v>
       </c>
-      <c r="E45" t="s">
-        <v>82</v>
-      </c>
       <c r="F45" s="5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="C46" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="D46" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="B46" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="C46" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="D46" s="6" t="s">
-        <v>106</v>
-      </c>
       <c r="F46" s="5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
@@ -1470,16 +1470,16 @@
         <v>20</v>
       </c>
       <c r="D48" t="s">
+        <v>54</v>
+      </c>
+      <c r="E48" t="s">
         <v>55</v>
       </c>
-      <c r="E48" t="s">
-        <v>56</v>
-      </c>
       <c r="F48" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G48" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
@@ -1493,13 +1493,13 @@
         <v>25</v>
       </c>
       <c r="D49" t="s">
+        <v>56</v>
+      </c>
+      <c r="E49" t="s">
         <v>57</v>
       </c>
-      <c r="E49" t="s">
-        <v>58</v>
-      </c>
       <c r="F49" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
@@ -1513,13 +1513,13 @@
         <v>25</v>
       </c>
       <c r="D50" t="s">
+        <v>58</v>
+      </c>
+      <c r="E50" t="s">
         <v>59</v>
       </c>
-      <c r="E50" t="s">
-        <v>60</v>
-      </c>
       <c r="F50" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
@@ -1533,13 +1533,13 @@
         <v>25</v>
       </c>
       <c r="D51" t="s">
+        <v>60</v>
+      </c>
+      <c r="E51" t="s">
         <v>61</v>
       </c>
-      <c r="E51" t="s">
-        <v>62</v>
-      </c>
       <c r="F51" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
@@ -1553,16 +1553,16 @@
         <v>20</v>
       </c>
       <c r="D52" t="s">
+        <v>62</v>
+      </c>
+      <c r="E52" t="s">
         <v>63</v>
       </c>
-      <c r="E52" t="s">
-        <v>64</v>
-      </c>
       <c r="F52" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G52" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
@@ -1576,10 +1576,10 @@
         <v>15</v>
       </c>
       <c r="D53" t="s">
+        <v>64</v>
+      </c>
+      <c r="E53" t="s">
         <v>65</v>
-      </c>
-      <c r="E53" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">

--- a/GenAI/ROADMAP-GenAI.xlsx
+++ b/GenAI/ROADMAP-GenAI.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ash\Desktop\educational\tut_youtube\GenAI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90744AC9-957C-417B-86BC-29D0F02CBBF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35254B7E-6410-413D-80BF-5A8DF7DF0DCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2490" yWindow="1320" windowWidth="25830" windowHeight="14160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="107">
   <si>
     <t>Week</t>
   </si>
@@ -45,18 +45,6 @@
     <t>What students will learn, outcomes, projects, why GenAI is important</t>
   </si>
   <si>
-    <t>What is GenAI</t>
-  </si>
-  <si>
-    <t>AI vs ML vs DL vs GenAI explained with simple examples</t>
-  </si>
-  <si>
-    <t>Real World Applications</t>
-  </si>
-  <si>
-    <t>Chatbots, content creation, coding, business use cases</t>
-  </si>
-  <si>
     <t>Demo Tools</t>
   </si>
   <si>
@@ -69,12 +57,6 @@
     <t>Neurons, weights, bias explained visually</t>
   </si>
   <si>
-    <t>Deep Learning Intuition</t>
-  </si>
-  <si>
-    <t>Why deep learning is needed for GenAI</t>
-  </si>
-  <si>
     <t xml:space="preserve"> NLP Basics </t>
   </si>
   <si>
@@ -282,12 +264,6 @@
     <t xml:space="preserve"> GPT, LLaMA overview, scale concept</t>
   </si>
   <si>
-    <t>Brief Overview of Gen AI</t>
-  </si>
-  <si>
-    <t>Foundation+Theory of GenAI(My addon)</t>
-  </si>
-  <si>
     <t>Ethical consideration of GenAI</t>
   </si>
   <si>
@@ -352,6 +328,24 @@
   </si>
   <si>
     <t xml:space="preserve"> Generate text, parameters (temperature, tokens, etc.) </t>
+  </si>
+  <si>
+    <t>AI vs ML vs DL vs GenAI explained with simple examples, Why deep learning is needed for GenAI</t>
+  </si>
+  <si>
+    <t>Examples of GenAI(My addon)</t>
+  </si>
+  <si>
+    <t>examples</t>
+  </si>
+  <si>
+    <t>Evolution AI and What is GenAI</t>
+  </si>
+  <si>
+    <t>Show in class</t>
+  </si>
+  <si>
+    <t>PDF for Hallucination  done</t>
   </si>
 </sst>
 </file>
@@ -695,7 +689,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H93"/>
+  <dimension ref="A1:H92"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="5"/>
@@ -722,16 +716,16 @@
         <v>1</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
@@ -762,50 +756,53 @@
         <v>20</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>6</v>
+        <v>104</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>7</v>
+        <v>101</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>85</v>
+        <v>103</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
@@ -813,16 +810,19 @@
         <v>1</v>
       </c>
       <c r="B6" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C6" s="4">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>9</v>
+        <v>7</v>
+      </c>
+      <c r="F6" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -830,90 +830,83 @@
         <v>1</v>
       </c>
       <c r="B7" s="4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C7" s="4">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>11</v>
+        <v>9</v>
+      </c>
+      <c r="F7" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="4">
-        <v>1</v>
-      </c>
-      <c r="B8" s="4">
-        <v>5</v>
-      </c>
-      <c r="C8" s="4">
-        <v>20</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F8" t="s">
-        <v>74</v>
-      </c>
+      <c r="A8" s="4"/>
+      <c r="B8" s="4"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="4">
         <v>1</v>
       </c>
-      <c r="B9" s="4">
-        <v>6</v>
-      </c>
-      <c r="C9" s="4">
-        <v>20</v>
-      </c>
+      <c r="B9" s="4"/>
+      <c r="C9" s="4"/>
       <c r="D9" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>15</v>
+        <v>98</v>
+      </c>
+      <c r="E9" s="3"/>
+      <c r="F9" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="4">
-        <v>1</v>
-      </c>
-      <c r="B10" s="4"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="3" t="s">
-        <v>106</v>
-      </c>
       <c r="E10" s="3"/>
-      <c r="F10" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="E11" s="3"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" s="5">
+        <v>2</v>
+      </c>
+      <c r="B12" s="5">
+        <v>7</v>
+      </c>
+      <c r="C12" s="5">
+        <v>20</v>
+      </c>
+      <c r="D12" t="s">
+        <v>10</v>
+      </c>
+      <c r="E12" t="s">
+        <v>11</v>
+      </c>
+      <c r="F12" t="s">
+        <v>89</v>
+      </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="5">
         <v>2</v>
       </c>
       <c r="B13" s="5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C13" s="5">
         <v>20</v>
       </c>
       <c r="D13" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E13" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F13" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
@@ -921,19 +914,19 @@
         <v>2</v>
       </c>
       <c r="B14" s="5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C14" s="5">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="D14" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E14" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F14" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
@@ -941,19 +934,19 @@
         <v>2</v>
       </c>
       <c r="B15" s="5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C15" s="5">
         <v>25</v>
       </c>
       <c r="D15" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E15" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F15" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
@@ -961,525 +954,531 @@
         <v>2</v>
       </c>
       <c r="B16" s="5">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C16" s="5">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D16" t="s">
+        <v>18</v>
+      </c>
+      <c r="E16" t="s">
+        <v>19</v>
+      </c>
+      <c r="F16" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D17"/>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" s="5">
+        <v>3</v>
+      </c>
+      <c r="B18" s="5">
+        <v>12</v>
+      </c>
+      <c r="C18" s="5">
+        <v>20</v>
+      </c>
+      <c r="D18" t="s">
+        <v>20</v>
+      </c>
+      <c r="E18" t="s">
+        <v>78</v>
+      </c>
+      <c r="F18" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D19" t="s">
+        <v>77</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" s="5">
+        <v>3</v>
+      </c>
+      <c r="B20" s="5">
+        <v>13</v>
+      </c>
+      <c r="C20" s="5">
+        <v>20</v>
+      </c>
+      <c r="D20" t="s">
+        <v>21</v>
+      </c>
+      <c r="E20" t="s">
         <v>22</v>
       </c>
-      <c r="E16" t="s">
-        <v>23</v>
-      </c>
-      <c r="F16" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="5">
-        <v>2</v>
-      </c>
-      <c r="B17" s="5">
-        <v>11</v>
-      </c>
-      <c r="C17" s="5">
-        <v>20</v>
-      </c>
-      <c r="D17" t="s">
-        <v>24</v>
-      </c>
-      <c r="E17" t="s">
-        <v>25</v>
-      </c>
-      <c r="F17" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="D18"/>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="5">
-        <v>3</v>
-      </c>
-      <c r="B19" s="5">
-        <v>12</v>
-      </c>
-      <c r="C19" s="5">
-        <v>20</v>
-      </c>
-      <c r="D19" t="s">
-        <v>26</v>
-      </c>
-      <c r="E19" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="D20" t="s">
-        <v>83</v>
-      </c>
-      <c r="E20" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="F20" s="5" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F20" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="5">
         <v>3</v>
       </c>
       <c r="B21" s="5">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="C21" s="5">
         <v>20</v>
       </c>
       <c r="D21" t="s">
-        <v>27</v>
+        <v>84</v>
       </c>
       <c r="E21" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="F21" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="5">
         <v>3</v>
       </c>
       <c r="B22" s="5">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C22" s="5">
         <v>20</v>
       </c>
       <c r="D22" t="s">
-        <v>92</v>
+        <v>44</v>
       </c>
       <c r="E22" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="F22" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="5">
         <v>3</v>
       </c>
       <c r="B23" s="5">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="C23" s="5">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="D23" t="s">
-        <v>50</v>
+        <v>23</v>
       </c>
       <c r="E23" t="s">
-        <v>51</v>
+        <v>24</v>
       </c>
       <c r="F23" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="5">
         <v>3</v>
       </c>
       <c r="B24" s="5">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C24" s="5">
         <v>25</v>
       </c>
       <c r="D24" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="E24" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="F24" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="5">
         <v>3</v>
       </c>
       <c r="B25" s="5">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C25" s="5">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D25" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="E25" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="F25" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="5">
-        <v>3</v>
-      </c>
-      <c r="B26" s="5">
-        <v>16</v>
-      </c>
-      <c r="C26" s="5">
-        <v>20</v>
-      </c>
-      <c r="D26" t="s">
-        <v>33</v>
-      </c>
-      <c r="E26" t="s">
-        <v>34</v>
-      </c>
-      <c r="F26" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="D27"/>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D26"/>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" s="5">
+        <v>4</v>
+      </c>
+      <c r="B27" s="5">
+        <v>17</v>
+      </c>
+      <c r="C27" s="5">
+        <v>20</v>
+      </c>
+      <c r="D27" t="s">
+        <v>29</v>
+      </c>
+      <c r="E27" t="s">
+        <v>30</v>
+      </c>
+      <c r="F27" t="s">
+        <v>65</v>
+      </c>
+      <c r="G27" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="5">
         <v>4</v>
       </c>
       <c r="B28" s="5">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C28" s="5">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="D28" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="E28" t="s">
-        <v>36</v>
+        <v>100</v>
       </c>
       <c r="F28" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="G28" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="5">
         <v>4</v>
       </c>
       <c r="B29" s="5">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C29" s="5">
         <v>25</v>
       </c>
       <c r="D29" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="E29" t="s">
-        <v>108</v>
+        <v>72</v>
       </c>
       <c r="F29" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="G29" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="5">
         <v>4</v>
       </c>
       <c r="B30" s="5">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C30" s="5">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D30" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="E30" t="s">
-        <v>78</v>
+        <v>34</v>
       </c>
       <c r="F30" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="G30" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="5">
         <v>4</v>
       </c>
       <c r="B31" s="5">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C31" s="5">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="D31" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="E31" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="F31" t="s">
-        <v>72</v>
-      </c>
-      <c r="G31" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="5">
         <v>4</v>
       </c>
       <c r="B32" s="5">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C32" s="5">
         <v>25</v>
       </c>
       <c r="D32" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E32" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="F32" t="s">
+        <v>65</v>
+      </c>
+      <c r="G32" t="s">
+        <v>63</v>
+      </c>
+      <c r="H32" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="5">
         <v>4</v>
       </c>
-      <c r="B33" s="5">
-        <v>22</v>
-      </c>
-      <c r="C33" s="5">
-        <v>25</v>
-      </c>
       <c r="D33" t="s">
-        <v>43</v>
-      </c>
-      <c r="E33" t="s">
-        <v>44</v>
+        <v>94</v>
       </c>
       <c r="F33" t="s">
-        <v>71</v>
-      </c>
-      <c r="G33" t="s">
-        <v>69</v>
-      </c>
-      <c r="H33" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="5">
         <v>4</v>
       </c>
-      <c r="D34" t="s">
-        <v>102</v>
+      <c r="D34"/>
+      <c r="E34" t="s">
+        <v>99</v>
       </c>
       <c r="F34" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A35" s="5">
-        <v>4</v>
-      </c>
+        <v>67</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="D35"/>
-      <c r="E35" t="s">
-        <v>107</v>
-      </c>
-      <c r="F35" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="D36"/>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="D37"/>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A37" s="5">
+        <v>5</v>
+      </c>
+      <c r="B37" s="5">
+        <v>23</v>
+      </c>
+      <c r="C37" s="5">
+        <v>20</v>
+      </c>
+      <c r="D37" t="s">
+        <v>39</v>
+      </c>
+      <c r="E37" t="s">
+        <v>40</v>
+      </c>
+      <c r="F37" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="5">
         <v>5</v>
       </c>
-      <c r="B38" s="5">
-        <v>23</v>
-      </c>
-      <c r="C38" s="5">
-        <v>20</v>
-      </c>
       <c r="D38" t="s">
-        <v>45</v>
-      </c>
-      <c r="E38" t="s">
-        <v>46</v>
+        <v>39</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>87</v>
       </c>
       <c r="G38" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="5">
         <v>5</v>
       </c>
       <c r="D39" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="G39" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="5">
         <v>5</v>
       </c>
+      <c r="B40" s="5">
+        <v>24</v>
+      </c>
+      <c r="C40" s="5">
+        <v>25</v>
+      </c>
       <c r="D40" t="s">
-        <v>45</v>
-      </c>
-      <c r="E40" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="G40" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+      <c r="E40" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="5">
         <v>5</v>
       </c>
-      <c r="B41" s="5">
-        <v>24</v>
-      </c>
-      <c r="C41" s="5">
-        <v>25</v>
-      </c>
       <c r="D41" t="s">
+        <v>92</v>
+      </c>
+      <c r="G41" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A43" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="B43" s="5">
+        <v>27</v>
+      </c>
+      <c r="C43" s="5">
+        <v>20</v>
+      </c>
+      <c r="D43" t="s">
+        <v>46</v>
+      </c>
+      <c r="E43" t="s">
         <v>47</v>
       </c>
-      <c r="E41" t="s">
+      <c r="F43" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A44" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="C44" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D44" t="s">
+        <v>74</v>
+      </c>
+      <c r="E44" t="s">
+        <v>75</v>
+      </c>
+      <c r="F44" s="5" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A45" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="C45" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="D45" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="F45" s="5" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D46"/>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A47" s="5">
+        <v>6</v>
+      </c>
+      <c r="B47" s="5">
+        <v>28</v>
+      </c>
+      <c r="C47" s="5">
+        <v>20</v>
+      </c>
+      <c r="D47" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A42" s="5">
-        <v>5</v>
-      </c>
-      <c r="D42" t="s">
-        <v>100</v>
-      </c>
-      <c r="G42" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A44" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="B44" s="5">
-        <v>27</v>
-      </c>
-      <c r="C44" s="5">
-        <v>20</v>
-      </c>
-      <c r="D44" t="s">
-        <v>52</v>
-      </c>
-      <c r="E44" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A45" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="C45" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="D45" t="s">
-        <v>80</v>
-      </c>
-      <c r="E45" t="s">
+      <c r="E47" t="s">
+        <v>49</v>
+      </c>
+      <c r="F47" t="s">
         <v>81</v>
       </c>
-      <c r="F45" s="5" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A46" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="C46" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="D46" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="F46" s="5" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="D47"/>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G47" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" s="5">
         <v>6</v>
       </c>
       <c r="B48" s="5">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C48" s="5">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="D48" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="E48" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="F48" t="s">
-        <v>89</v>
-      </c>
-      <c r="G48" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
@@ -1487,19 +1486,19 @@
         <v>6</v>
       </c>
       <c r="B49" s="5">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C49" s="5">
         <v>25</v>
       </c>
       <c r="D49" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="E49" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="F49" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
@@ -1507,19 +1506,19 @@
         <v>6</v>
       </c>
       <c r="B50" s="5">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C50" s="5">
         <v>25</v>
       </c>
       <c r="D50" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="E50" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="F50" t="s">
-        <v>89</v>
+        <v>65</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
@@ -1527,19 +1526,22 @@
         <v>6</v>
       </c>
       <c r="B51" s="5">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C51" s="5">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D51" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="E51" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="F51" t="s">
-        <v>71</v>
+        <v>65</v>
+      </c>
+      <c r="G51" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
@@ -1547,40 +1549,20 @@
         <v>6</v>
       </c>
       <c r="B52" s="5">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C52" s="5">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="D52" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="E52" t="s">
-        <v>63</v>
-      </c>
-      <c r="F52" t="s">
-        <v>71</v>
-      </c>
-      <c r="G52" t="s">
-        <v>79</v>
+        <v>59</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A53" s="5">
-        <v>6</v>
-      </c>
-      <c r="B53" s="5">
-        <v>33</v>
-      </c>
-      <c r="C53" s="5">
-        <v>15</v>
-      </c>
-      <c r="D53" t="s">
-        <v>64</v>
-      </c>
-      <c r="E53" t="s">
-        <v>65</v>
-      </c>
+      <c r="D53"/>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="D54"/>
@@ -1698,9 +1680,6 @@
     </row>
     <row r="92" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D92"/>
-    </row>
-    <row r="93" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D93"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
